--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -1,72 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/seed_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_05295719556F880E62355476585DCE3A87473687" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28E81142-65EC-49FC-BF3B-B262AB1E5BDF}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>latestp1</t>
-  </si>
-  <si>
-    <t>latestp2</t>
-  </si>
-  <si>
-    <t>latestp3</t>
-  </si>
-  <si>
-    <t>latestp4</t>
-  </si>
-  <si>
-    <t>latestpw</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,62 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -418,47 +420,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>latestp1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latestp2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>latestp3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>latestp4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>latestpw</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>July2025p4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>July2025pw</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>July2025_score</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>August2026p1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>August2026p2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>August2026p3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>August2026p4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>August2026pw</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>August2026_score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ava.canning</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Isabella Merriman</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Margaret O'Donoghue</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,36 @@
           <t>August2026_score</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>May2026p1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>May2026p2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>May2026p3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>May2026p4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>May2026pw</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>May2026_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,12 +558,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ava Canning</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Valmai Gee</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -543,12 +573,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Margaret O'Donoghue</t>
+          <t>Sadhbh Smyth</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jenny Sparrow</t>
+          <t>Roisin Hickey</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -579,12 +609,112 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Isabel Saeed-Maguire</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Valmai Gee</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lauren Torpey</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Roisin Hickey</t>
+        </is>
+      </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Amy Kenealy</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Roisin Hickey</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Lavanya Rajesh</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>jenny.sparrow</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Alex Sheedy</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aisling Dunne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Emily Bowe</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,6 +718,36 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mark.canning</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -558,27 +558,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Isabel Saeed-Maguire</t>
+          <t>Ava Canning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Valmai Gee</t>
+          <t>Amy Kenealy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Roisin Hickey</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Lavanya Rajesh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Roisin Hickey</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -672,11 +672,31 @@
           <t>jenny.sparrow</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alex Sheedy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sue O'Connor</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aisling O'Kelly</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aisling Dunne</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Emily Bowe</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -688,7 +708,9 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>Alex Sheedy</t>
@@ -715,7 +737,7 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="4">
@@ -724,11 +746,31 @@
           <t>mark.canning</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -740,13 +782,17 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>May2026_score</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -664,6 +669,9 @@
       </c>
       <c r="X2" t="n">
         <v>30</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="3">
@@ -739,6 +747,9 @@
       <c r="X3" t="n">
         <v>447.5</v>
       </c>
+      <c r="Y3" t="n">
+        <v>576</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -793,6 +804,9 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,41 @@
           <t>May2026</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>June2026p1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>June2026p2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>June2026p3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>June2026p4</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>June2026pw</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>June2026_score</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>June2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -668,10 +703,21 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>453</v>
       </c>
       <c r="Y2" t="n">
-        <v>299</v>
+        <v>453</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -745,10 +791,21 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>447.5</v>
+        <v>836</v>
       </c>
       <c r="Y3" t="n">
-        <v>576</v>
+        <v>836</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -759,27 +816,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Beth Dimond</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Sophia Nulty</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Sadhbh Smyth</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Rachel Sparrow</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -796,15 +853,66 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Alex Sheedy</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Beth Dimond</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sophia Nulty</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
       <c r="X4" t="n">
+        <v>884</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>884</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Ava Canning</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Amy Kenealy</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Katie Dagostino</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Zara Deacon</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Ava McCormack</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AF4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/picks.xlsx
+++ b/data/picks.xlsx
@@ -708,11 +708,31 @@
       <c r="Y2" t="n">
         <v>453</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Jenny Sparrow</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Amy Kenealy</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Catherine Nulty</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ruth McGonnell</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Laura Delany</t>
+        </is>
+      </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
